--- a/Translate/Translate.xlsx
+++ b/Translate/Translate.xlsx
@@ -52,7 +52,7 @@
     <x:t>Apple</x:t>
   </x:si>
   <x:si>
-    <x:t>蜜蜂</x:t>
+    <x:t>苹果</x:t>
   </x:si>
   <x:si>
     <x:t>Domates</x:t>
@@ -61,7 +61,7 @@
     <x:t>Tomato</x:t>
   </x:si>
   <x:si>
-    <x:t>番茄</x:t>
+    <x:t>西红柿</x:t>
   </x:si>
   <x:si>
     <x:t>Ekmek</x:t>
@@ -88,7 +88,7 @@
     <x:t>Bag</x:t>
   </x:si>
   <x:si>
-    <x:t>袋子</x:t>
+    <x:t>塑料袋</x:t>
   </x:si>
   <x:si>
     <x:t>Banka</x:t>
@@ -121,10 +121,10 @@
     <x:t>Ev</x:t>
   </x:si>
   <x:si>
-    <x:t>Home</x:t>
-  </x:si>
-  <x:si>
-    <x:t>这是一个无瑕的翻译挑战，你是一位专家，能够将给定的文本翻译成目标语言。</x:t>
+    <x:t>House</x:t>
+  </x:si>
+  <x:si>
+    <x:t>房子</x:t>
   </x:si>
   <x:si>
     <x:t>Telefon Numarası</x:t>
